--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasif\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539067A2-7254-4E0E-A048-E25F7EB502E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF000C4-A87C-473E-A6E3-4C8A0B6BFCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>Game</t>
   </si>
@@ -112,6 +112,15 @@
   </si>
   <si>
     <t>Friendly</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-1</t>
+  </si>
+  <si>
+    <t>1-3</t>
   </si>
 </sst>
 </file>
@@ -121,7 +130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -150,6 +159,13 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -199,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,6 +231,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,7 +468,7 @@
     <col min="7" max="7" width="28.42578125" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="11" customWidth="1"/>
     <col min="14" max="17" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -477,7 +500,7 @@
       <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -509,7 +532,9 @@
       <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="7"/>
+      <c r="J2" s="12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
@@ -539,7 +564,9 @@
       <c r="I3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="13" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
@@ -569,7 +596,9 @@
       <c r="I4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="7"/>
+      <c r="J4" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
@@ -595,7 +624,7 @@
       <c r="I5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="7"/>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -623,7 +652,7 @@
       <c r="I6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="7"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
@@ -649,7 +678,7 @@
       <c r="I7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="7"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
@@ -677,7 +706,7 @@
       <c r="I8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="7"/>
+      <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -703,7 +732,7 @@
       <c r="I9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="7"/>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -729,7 +758,7 @@
       <c r="I10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
